--- a/artfynd/A 42644-2021 artfynd.xlsx
+++ b/artfynd/A 42644-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42644-2021 artfynd.xlsx
+++ b/artfynd/A 42644-2021 artfynd.xlsx
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>83326612</v>
+        <v>732406</v>
       </c>
       <c r="B2" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>2779</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>VGL Träd ID: 22031, Vg</t>
+          <t>Horreds-Bosgården, träd 21204 (lönn), Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>346073.9747256893</v>
+        <v>346046</v>
       </c>
       <c r="R2" t="n">
-        <v>6357708.224997433</v>
+        <v>6357530</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,29 +738,14 @@
           <t>Horred</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>04392863-6ACC-4634-8E5C-4BA8D6698427</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
           <t>2007-10-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2007-10-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,6 +757,14 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>1 substratenheter # lönn</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -789,12 +773,12 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars Sjögren, Lena Smith</t>
+          <t>Lena Smith</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Trädportalen</t>
+          <t>Epifyt-inv. Särskilt skyddsvärda träd 2005-2007</t>
         </is>
       </c>
     </row>
@@ -803,12 +787,7 @@
         <v>1866389</v>
       </c>
       <c r="B3" t="n">
-        <v>73507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>346045.5359181814</v>
+        <v>346046</v>
       </c>
       <c r="R3" t="n">
-        <v>6357527.764564584</v>
+        <v>6357528</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,19 +852,9 @@
           <t>2007-10-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2007-10-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -929,15 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>732406</v>
+        <v>1866390</v>
       </c>
       <c r="B4" t="n">
-        <v>92939</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,34 +909,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2779</v>
+        <v>6428</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Horreds-Bosgården, träd 21204 (lönn), Vg</t>
+          <t>Horreds-Bosgården, träd 22454 (ek), Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>346046.157646167</v>
+        <v>346047</v>
       </c>
       <c r="R4" t="n">
-        <v>6357529.902301227</v>
+        <v>6357529</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,19 +966,14 @@
           <t>2007-10-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2007-10-15</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Inventerad av Elisabeth Ryberg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,7 +990,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>1 substratenheter # lönn</t>
+          <t>1 substratenheter # ek</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1042,7 +1001,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lena Smith</t>
+          <t>Via Lars Sjögren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1053,53 +1012,52 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1866390</v>
+        <v>83326612</v>
       </c>
       <c r="B5" t="n">
-        <v>73507</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6428</v>
+        <v>220785</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Horreds-Bosgården, träd 22454 (ek), Vg</t>
+          <t>VGL Träd ID: 22031, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>346047.1982207061</v>
+        <v>346074</v>
       </c>
       <c r="R5" t="n">
-        <v>6357528.782613302</v>
+        <v>6357708</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1121,29 +1079,19 @@
           <t>Horred</t>
         </is>
       </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>04392863-6ACC-4634-8E5C-4BA8D6698427</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr">
         <is>
           <t>2007-10-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2007-10-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Inventerad av Elisabeth Ryberg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,14 +1103,6 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AN5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>1 substratenheter # ek</t>
-        </is>
-      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
@@ -1171,12 +1111,12 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Lars Sjögren</t>
+          <t>Lars Sjögren, Lena Smith</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Epifyt-inv. Särskilt skyddsvärda träd 2005-2007</t>
+          <t>Trädportalen</t>
         </is>
       </c>
     </row>
